--- a/推荐订单占比 (19).xlsx
+++ b/推荐订单占比 (19).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jiangziyi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jiangziyi\Downloads\car-owner-dashboard-github-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8426B357-A33F-412F-90EF-754EBD8319DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878EE5EC-E50F-47AC-8ABD-CAD125D92D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,7 +127,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="###,###,###,###,###,##0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -192,6 +192,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -245,12 +252,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -287,8 +297,30 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -629,15 +661,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="7">
-        <v>12837</v>
+        <v>29300</v>
       </c>
       <c r="C2" s="7">
         <f>SUM(C3:C25)</f>
-        <v>2617</v>
-      </c>
-      <c r="D2" s="7">
+        <v>6937</v>
+      </c>
+      <c r="D2" s="18">
         <f>C2/B2</f>
-        <v>0.20386383111318843</v>
+        <v>0.23675767918088736</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="32" customHeight="1">
@@ -645,14 +677,14 @@
         <v>3</v>
       </c>
       <c r="B3" s="8">
-        <v>255</v>
+        <v>580</v>
       </c>
       <c r="C3" s="9">
-        <v>72</v>
-      </c>
-      <c r="D3" s="8">
-        <f t="shared" ref="D3:D25" si="0">C3/B3</f>
-        <v>0.28235294117647058</v>
+        <v>168</v>
+      </c>
+      <c r="D3" s="12">
+        <f>C3/B3</f>
+        <v>0.28965517241379313</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32" customHeight="1">
@@ -660,14 +692,14 @@
         <v>4</v>
       </c>
       <c r="B4" s="10">
-        <v>682</v>
+        <v>1300</v>
       </c>
       <c r="C4" s="11">
-        <v>150</v>
-      </c>
-      <c r="D4" s="10">
-        <f t="shared" si="0"/>
-        <v>0.21994134897360704</v>
+        <v>345</v>
+      </c>
+      <c r="D4" s="13">
+        <f t="shared" ref="D4:D25" si="0">C4/B4</f>
+        <v>0.26538461538461539</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="32" customHeight="1">
@@ -675,14 +707,14 @@
         <v>5</v>
       </c>
       <c r="B5" s="8">
-        <v>145</v>
+        <v>382</v>
       </c>
       <c r="C5" s="9">
-        <v>40</v>
-      </c>
-      <c r="D5" s="8">
-        <f t="shared" si="0"/>
-        <v>0.27586206896551724</v>
+        <v>108</v>
+      </c>
+      <c r="D5" s="12">
+        <f t="shared" si="0"/>
+        <v>0.28272251308900526</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="32" customHeight="1">
@@ -690,14 +722,14 @@
         <v>6</v>
       </c>
       <c r="B6" s="10">
-        <v>247</v>
+        <v>592</v>
       </c>
       <c r="C6" s="11">
-        <v>59</v>
-      </c>
-      <c r="D6" s="10">
-        <f t="shared" si="0"/>
-        <v>0.23886639676113361</v>
+        <v>133</v>
+      </c>
+      <c r="D6" s="13">
+        <f t="shared" si="0"/>
+        <v>0.22466216216216217</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" customHeight="1">
@@ -705,14 +737,14 @@
         <v>7</v>
       </c>
       <c r="B7" s="8">
-        <v>464</v>
+        <v>1128</v>
       </c>
       <c r="C7" s="9">
-        <v>110</v>
-      </c>
-      <c r="D7" s="8">
-        <f t="shared" si="0"/>
-        <v>0.23706896551724138</v>
+        <v>312</v>
+      </c>
+      <c r="D7" s="12">
+        <f t="shared" si="0"/>
+        <v>0.27659574468085107</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" customHeight="1">
@@ -720,14 +752,14 @@
         <v>8</v>
       </c>
       <c r="B8" s="10">
-        <v>460</v>
+        <v>1085</v>
       </c>
       <c r="C8" s="11">
-        <v>112</v>
-      </c>
-      <c r="D8" s="10">
-        <f t="shared" si="0"/>
-        <v>0.24347826086956523</v>
+        <v>305</v>
+      </c>
+      <c r="D8" s="13">
+        <f t="shared" si="0"/>
+        <v>0.28110599078341014</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="32" customHeight="1">
@@ -735,14 +767,14 @@
         <v>9</v>
       </c>
       <c r="B9" s="8">
-        <v>1919</v>
+        <v>3863</v>
       </c>
       <c r="C9" s="9">
-        <v>420</v>
-      </c>
-      <c r="D9" s="8">
-        <f t="shared" si="0"/>
-        <v>0.21886399166232412</v>
+        <v>1012</v>
+      </c>
+      <c r="D9" s="12">
+        <f t="shared" si="0"/>
+        <v>0.26197256018638365</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="32" customHeight="1">
@@ -750,14 +782,14 @@
         <v>10</v>
       </c>
       <c r="B10" s="10">
-        <v>610</v>
+        <v>1459</v>
       </c>
       <c r="C10" s="11">
-        <v>155</v>
-      </c>
-      <c r="D10" s="10">
-        <f t="shared" si="0"/>
-        <v>0.25409836065573771</v>
+        <v>397</v>
+      </c>
+      <c r="D10" s="13">
+        <f t="shared" si="0"/>
+        <v>0.27210418094585331</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="32" customHeight="1">
@@ -765,14 +797,14 @@
         <v>11</v>
       </c>
       <c r="B11" s="8">
-        <v>280</v>
+        <v>766</v>
       </c>
       <c r="C11" s="9">
-        <v>66</v>
-      </c>
-      <c r="D11" s="8">
-        <f t="shared" si="0"/>
-        <v>0.23571428571428571</v>
+        <v>192</v>
+      </c>
+      <c r="D11" s="12">
+        <f t="shared" si="0"/>
+        <v>0.25065274151436029</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="32" customHeight="1">
@@ -780,14 +812,14 @@
         <v>12</v>
       </c>
       <c r="B12" s="10">
-        <v>1256</v>
+        <v>2915</v>
       </c>
       <c r="C12" s="11">
-        <v>274</v>
-      </c>
-      <c r="D12" s="10">
-        <f t="shared" si="0"/>
-        <v>0.21815286624203822</v>
+        <v>741</v>
+      </c>
+      <c r="D12" s="13">
+        <f t="shared" si="0"/>
+        <v>0.25420240137221267</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="32" customHeight="1">
@@ -795,14 +827,14 @@
         <v>13</v>
       </c>
       <c r="B13" s="8">
-        <v>169</v>
+        <v>399</v>
       </c>
       <c r="C13" s="9">
-        <v>39</v>
-      </c>
-      <c r="D13" s="8">
-        <f t="shared" si="0"/>
-        <v>0.23076923076923078</v>
+        <v>106</v>
+      </c>
+      <c r="D13" s="12">
+        <f t="shared" si="0"/>
+        <v>0.26566416040100249</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="32" customHeight="1">
@@ -810,14 +842,14 @@
         <v>14</v>
       </c>
       <c r="B14" s="10">
-        <v>1219</v>
+        <v>2794</v>
       </c>
       <c r="C14" s="11">
-        <v>243</v>
-      </c>
-      <c r="D14" s="10">
-        <f t="shared" si="0"/>
-        <v>0.19934372436423298</v>
+        <v>628</v>
+      </c>
+      <c r="D14" s="13">
+        <f t="shared" si="0"/>
+        <v>0.22476735862562633</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="32" customHeight="1">
@@ -825,14 +857,14 @@
         <v>15</v>
       </c>
       <c r="B15" s="8">
-        <v>550</v>
+        <v>1713</v>
       </c>
       <c r="C15" s="9">
-        <v>107</v>
-      </c>
-      <c r="D15" s="8">
-        <f t="shared" si="0"/>
-        <v>0.19454545454545455</v>
+        <v>409</v>
+      </c>
+      <c r="D15" s="12">
+        <f t="shared" si="0"/>
+        <v>0.23876240513718622</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="32" customHeight="1">
@@ -840,14 +872,14 @@
         <v>16</v>
       </c>
       <c r="B16" s="10">
-        <v>1030</v>
+        <v>2154</v>
       </c>
       <c r="C16" s="11">
-        <v>209</v>
-      </c>
-      <c r="D16" s="10">
-        <f t="shared" si="0"/>
-        <v>0.20291262135922331</v>
+        <v>500</v>
+      </c>
+      <c r="D16" s="13">
+        <f t="shared" si="0"/>
+        <v>0.23212627669452182</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="32" customHeight="1">
@@ -855,14 +887,14 @@
         <v>17</v>
       </c>
       <c r="B17" s="8">
-        <v>705</v>
+        <v>1404</v>
       </c>
       <c r="C17" s="9">
-        <v>132</v>
-      </c>
-      <c r="D17" s="8">
-        <f t="shared" si="0"/>
-        <v>0.18723404255319148</v>
+        <v>310</v>
+      </c>
+      <c r="D17" s="12">
+        <f t="shared" si="0"/>
+        <v>0.22079772079772081</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="32" customHeight="1">
@@ -870,14 +902,14 @@
         <v>18</v>
       </c>
       <c r="B18" s="10">
-        <v>421</v>
+        <v>1044</v>
       </c>
       <c r="C18" s="11">
-        <v>85</v>
-      </c>
-      <c r="D18" s="10">
-        <f t="shared" si="0"/>
-        <v>0.20190023752969122</v>
+        <v>276</v>
+      </c>
+      <c r="D18" s="13">
+        <f t="shared" si="0"/>
+        <v>0.26436781609195403</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="32" customHeight="1">
@@ -885,14 +917,14 @@
         <v>19</v>
       </c>
       <c r="B19" s="8">
-        <v>225</v>
+        <v>577</v>
       </c>
       <c r="C19" s="9">
-        <v>36</v>
-      </c>
-      <c r="D19" s="8">
-        <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>116</v>
+      </c>
+      <c r="D19" s="12">
+        <f t="shared" si="0"/>
+        <v>0.20103986135181975</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="32" customHeight="1">
@@ -900,14 +932,14 @@
         <v>20</v>
       </c>
       <c r="B20" s="10">
-        <v>253</v>
+        <v>578</v>
       </c>
       <c r="C20" s="11">
-        <v>49</v>
-      </c>
-      <c r="D20" s="10">
-        <f t="shared" si="0"/>
-        <v>0.19367588932806323</v>
+        <v>116</v>
+      </c>
+      <c r="D20" s="13">
+        <f t="shared" si="0"/>
+        <v>0.20069204152249134</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="32" customHeight="1">
@@ -915,14 +947,14 @@
         <v>21</v>
       </c>
       <c r="B21" s="8">
-        <v>375</v>
+        <v>874</v>
       </c>
       <c r="C21" s="9">
-        <v>60</v>
-      </c>
-      <c r="D21" s="8">
-        <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>179</v>
+      </c>
+      <c r="D21" s="12">
+        <f t="shared" si="0"/>
+        <v>0.20480549199084669</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="32" customHeight="1">
@@ -930,14 +962,14 @@
         <v>22</v>
       </c>
       <c r="B22" s="10">
-        <v>599</v>
+        <v>1498</v>
       </c>
       <c r="C22" s="11">
-        <v>93</v>
-      </c>
-      <c r="D22" s="10">
-        <f t="shared" si="0"/>
-        <v>0.15525876460767946</v>
+        <v>231</v>
+      </c>
+      <c r="D22" s="13">
+        <f t="shared" si="0"/>
+        <v>0.1542056074766355</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="32" customHeight="1">
@@ -945,14 +977,14 @@
         <v>23</v>
       </c>
       <c r="B23" s="8">
-        <v>208</v>
+        <v>533</v>
       </c>
       <c r="C23" s="9">
-        <v>27</v>
-      </c>
-      <c r="D23" s="8">
-        <f t="shared" si="0"/>
-        <v>0.12980769230769232</v>
+        <v>97</v>
+      </c>
+      <c r="D23" s="12">
+        <f t="shared" si="0"/>
+        <v>0.18198874296435272</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="32" customHeight="1">
@@ -960,14 +992,14 @@
         <v>24</v>
       </c>
       <c r="B24" s="6">
-        <v>219</v>
-      </c>
-      <c r="C24" s="3">
-        <v>30</v>
-      </c>
-      <c r="D24" s="6">
-        <f t="shared" si="0"/>
-        <v>0.13698630136986301</v>
+        <v>549</v>
+      </c>
+      <c r="C24" s="16">
+        <v>99</v>
+      </c>
+      <c r="D24" s="14">
+        <f t="shared" si="0"/>
+        <v>0.18032786885245902</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="32" customHeight="1">
@@ -975,14 +1007,14 @@
         <v>25</v>
       </c>
       <c r="B25" s="5">
-        <v>339</v>
-      </c>
-      <c r="C25" s="4">
-        <v>49</v>
-      </c>
-      <c r="D25" s="5">
-        <f t="shared" si="0"/>
-        <v>0.14454277286135694</v>
+        <v>880</v>
+      </c>
+      <c r="C25" s="17">
+        <v>157</v>
+      </c>
+      <c r="D25" s="15">
+        <f t="shared" si="0"/>
+        <v>0.17840909090909091</v>
       </c>
     </row>
   </sheetData>
